--- a/artfynd/A 15149-2025 artfynd.xlsx
+++ b/artfynd/A 15149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133509394</v>
       </c>
       <c r="B2" t="n">
-        <v>57971</v>
+        <v>57978</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 15149-2025 artfynd.xlsx
+++ b/artfynd/A 15149-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133509394</v>
       </c>
       <c r="B2" t="n">
-        <v>57978</v>
+        <v>57988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
